--- a/BRIN 3219/Septiembre/BRIN3219-EXPENSAS-Septiembre.xlsx
+++ b/BRIN 3219/Septiembre/BRIN3219-EXPENSAS-Septiembre.xlsx
@@ -5,21 +5,21 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BRIN 3219\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BRIN 3219\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B46DC62E-8C68-4AFD-B861-6B6EE118809F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A12A539-E23F-4F83-AC6F-24D5C58A4DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilla" sheetId="1" r:id="rId1"/>
-    <sheet name="EXTRAORDINARIAS" sheetId="28" r:id="rId2"/>
-    <sheet name="RESUMEN" sheetId="27" r:id="rId3"/>
+    <sheet name="RESUMEN" sheetId="27" r:id="rId1"/>
+    <sheet name="Planilla" sheetId="1" r:id="rId2"/>
+    <sheet name="EXTRAORDINARIAS" sheetId="28" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Planilla!$A$1:$N$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">RESUMEN!$A$1:$H$100</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$N$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$98</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="156">
   <si>
     <t>U.F.</t>
   </si>
@@ -496,12 +496,6 @@
   </si>
   <si>
     <t>AYSA</t>
-  </si>
-  <si>
-    <t>Destapacion cloacal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Megasec Recarga de matafuegos </t>
   </si>
   <si>
     <t>Dr. Sarro Murillo escrito</t>
@@ -533,7 +527,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -738,13 +732,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1325,7 +1312,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="239">
+  <cellXfs count="234">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1614,18 +1601,8 @@
     </xf>
     <xf numFmtId="164" fontId="17" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1644,12 +1621,81 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1674,12 +1720,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1689,21 +1729,6 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1713,76 +1738,25 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -1803,6 +1777,60 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>130966</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>71438</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>552449</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>134324</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="11023" r="10240"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="130966" y="71438"/>
+          <a:ext cx="3131346" cy="1622605"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1857,7 +1885,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1901,60 +1929,6 @@
         <a:xfrm>
           <a:off x="2076450" y="314325"/>
           <a:ext cx="2266950" cy="1027859"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>130966</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>71438</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>552449</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>134324</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect l="11023" r="10240"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="130966" y="71438"/>
-          <a:ext cx="3131346" cy="1622605"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2228,23 +2202,1342 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:K103"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="8"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="9"/>
+    </row>
+    <row r="2" spans="1:9" ht="48" customHeight="1">
+      <c r="A2" s="10"/>
+      <c r="D2" s="184"/>
+      <c r="E2" s="185"/>
+      <c r="F2" s="185"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="186"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="10"/>
+      <c r="D3" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="215">
+        <v>1153202676</v>
+      </c>
+      <c r="F3" s="215"/>
+      <c r="G3" s="215"/>
+      <c r="H3" s="216"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="10"/>
+      <c r="D4" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="10"/>
+      <c r="D5" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="56">
+        <v>30707328890</v>
+      </c>
+      <c r="H5" s="11"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="10"/>
+      <c r="D6" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H6" s="11"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="10"/>
+      <c r="H7" s="11"/>
+    </row>
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="18.75">
+      <c r="A8" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="90" t="s">
+        <v>153</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="H8" s="20"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="8"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="9"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A11" s="15"/>
+      <c r="E11" s="14"/>
+      <c r="H11" s="11"/>
+    </row>
+    <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
+      <c r="A12" s="193"/>
+      <c r="B12" s="194"/>
+      <c r="C12" s="194"/>
+      <c r="D12" s="194"/>
+      <c r="E12" s="194"/>
+      <c r="F12" s="194"/>
+      <c r="G12" s="194"/>
+      <c r="H12" s="195"/>
+    </row>
+    <row r="13" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A13" s="12"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="13"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.75">
+      <c r="A14" s="219" t="s">
+        <v>128</v>
+      </c>
+      <c r="B14" s="219"/>
+      <c r="C14" s="219"/>
+      <c r="D14" s="219"/>
+      <c r="E14" s="219"/>
+      <c r="F14" s="219"/>
+      <c r="G14" s="219"/>
+      <c r="H14" s="219"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="227" t="s">
+        <v>149</v>
+      </c>
+      <c r="B15" s="141"/>
+      <c r="C15" s="141"/>
+      <c r="D15" s="141"/>
+      <c r="E15" s="141"/>
+      <c r="F15" s="141"/>
+      <c r="G15" s="141"/>
+      <c r="H15" s="74">
+        <v>324630.59999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="227" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="141"/>
+      <c r="C16" s="141"/>
+      <c r="D16" s="141"/>
+      <c r="E16" s="141"/>
+      <c r="F16" s="141"/>
+      <c r="G16" s="141"/>
+      <c r="H16" s="74">
+        <v>-51129.33</v>
+      </c>
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="227" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="141"/>
+      <c r="C17" s="141"/>
+      <c r="D17" s="141"/>
+      <c r="E17" s="141"/>
+      <c r="F17" s="141"/>
+      <c r="G17" s="141"/>
+      <c r="H17" s="74">
+        <v>0.73</v>
+      </c>
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="227" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="141"/>
+      <c r="C18" s="141"/>
+      <c r="D18" s="141"/>
+      <c r="E18" s="141"/>
+      <c r="F18" s="141"/>
+      <c r="G18" s="141"/>
+      <c r="H18" s="74">
+        <f>SUM(H15:H17)</f>
+        <v>273501.99999999994</v>
+      </c>
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" spans="1:9" ht="0.75" customHeight="1">
+      <c r="A19" s="228" t="s">
+        <v>132</v>
+      </c>
+      <c r="B19" s="228"/>
+      <c r="C19" s="228"/>
+      <c r="D19" s="228"/>
+      <c r="E19" s="228"/>
+      <c r="F19" s="228"/>
+      <c r="G19" s="228"/>
+      <c r="H19" s="228"/>
+    </row>
+    <row r="20" spans="1:9" hidden="1">
+      <c r="A20" s="227" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" s="141"/>
+      <c r="C20" s="141"/>
+      <c r="D20" s="141"/>
+      <c r="E20" s="141"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="141"/>
+      <c r="H20" s="74"/>
+    </row>
+    <row r="21" spans="1:9" hidden="1">
+      <c r="A21" s="227"/>
+      <c r="B21" s="141"/>
+      <c r="C21" s="141"/>
+      <c r="D21" s="141"/>
+      <c r="E21" s="141"/>
+      <c r="F21" s="141"/>
+      <c r="G21" s="141"/>
+      <c r="H21" s="74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" hidden="1">
+      <c r="A22" s="227"/>
+      <c r="B22" s="141"/>
+      <c r="C22" s="141"/>
+      <c r="D22" s="141"/>
+      <c r="E22" s="141"/>
+      <c r="F22" s="141"/>
+      <c r="G22" s="141"/>
+      <c r="H22" s="74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" hidden="1">
+      <c r="A23" s="227"/>
+      <c r="B23" s="141"/>
+      <c r="C23" s="141"/>
+      <c r="D23" s="141"/>
+      <c r="E23" s="141"/>
+      <c r="F23" s="141"/>
+      <c r="G23" s="141"/>
+      <c r="H23" s="74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" hidden="1">
+      <c r="A24" s="227" t="s">
+        <v>133</v>
+      </c>
+      <c r="B24" s="141"/>
+      <c r="C24" s="141"/>
+      <c r="D24" s="141"/>
+      <c r="E24" s="141"/>
+      <c r="F24" s="141"/>
+      <c r="G24" s="141"/>
+      <c r="H24" s="74"/>
+    </row>
+    <row r="25" spans="1:9" hidden="1">
+      <c r="A25" s="227" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" s="141"/>
+      <c r="C25" s="141"/>
+      <c r="D25" s="141"/>
+      <c r="E25" s="141"/>
+      <c r="F25" s="141"/>
+      <c r="G25" s="141"/>
+      <c r="H25" s="74"/>
+    </row>
+    <row r="26" spans="1:9" hidden="1">
+      <c r="A26" s="227" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="141"/>
+      <c r="C26" s="141"/>
+      <c r="D26" s="141"/>
+      <c r="E26" s="141"/>
+      <c r="F26" s="141"/>
+      <c r="G26" s="141"/>
+      <c r="H26" s="70">
+        <f>SUM(H20:H25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="229" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" s="229"/>
+      <c r="C27" s="229"/>
+      <c r="D27" s="229"/>
+      <c r="E27" s="229"/>
+      <c r="F27" s="229"/>
+      <c r="G27" s="229"/>
+      <c r="H27" s="229"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="141" t="s">
+        <v>145</v>
+      </c>
+      <c r="B28" s="141"/>
+      <c r="C28" s="141"/>
+      <c r="D28" s="141"/>
+      <c r="E28" s="141"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="141"/>
+      <c r="H28" s="74">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="141"/>
+      <c r="B29" s="141"/>
+      <c r="C29" s="141"/>
+      <c r="D29" s="141"/>
+      <c r="E29" s="141"/>
+      <c r="F29" s="141"/>
+      <c r="G29" s="141"/>
+      <c r="H29" s="74"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="141" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="141"/>
+      <c r="C30" s="141"/>
+      <c r="D30" s="141"/>
+      <c r="E30" s="141"/>
+      <c r="F30" s="141"/>
+      <c r="G30" s="141"/>
+      <c r="H30" s="74">
+        <f>SUM(H28:H29)</f>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A31" s="230" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="230"/>
+      <c r="C31" s="230"/>
+      <c r="D31" s="230"/>
+      <c r="E31" s="230"/>
+      <c r="F31" s="230"/>
+      <c r="G31" s="230"/>
+      <c r="H31" s="230"/>
+    </row>
+    <row r="32" spans="1:9" hidden="1">
+      <c r="A32" s="227"/>
+      <c r="B32" s="141"/>
+      <c r="C32" s="141"/>
+      <c r="D32" s="141"/>
+      <c r="E32" s="141"/>
+      <c r="F32" s="141"/>
+      <c r="G32" s="141"/>
+      <c r="H32" s="74"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="227" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="231"/>
+      <c r="C33" s="141"/>
+      <c r="D33" s="141"/>
+      <c r="E33" s="141"/>
+      <c r="F33" s="141"/>
+      <c r="G33" s="141"/>
+      <c r="H33" s="74">
+        <f>14146.69+1571.86+33034.56</f>
+        <v>48753.11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="141" t="s">
+        <v>146</v>
+      </c>
+      <c r="B34" s="141"/>
+      <c r="C34" s="141"/>
+      <c r="D34" s="141"/>
+      <c r="E34" s="141"/>
+      <c r="F34" s="141"/>
+      <c r="G34" s="141"/>
+      <c r="H34" s="74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="141" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" s="141"/>
+      <c r="C35" s="141"/>
+      <c r="D35" s="141"/>
+      <c r="E35" s="141"/>
+      <c r="F35" s="141"/>
+      <c r="G35" s="141"/>
+      <c r="H35" s="74">
+        <f>SUM(H32:H34)</f>
+        <v>48753.11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="230" t="s">
+        <v>137</v>
+      </c>
+      <c r="B36" s="230"/>
+      <c r="C36" s="230"/>
+      <c r="D36" s="230"/>
+      <c r="E36" s="230"/>
+      <c r="F36" s="230"/>
+      <c r="G36" s="230"/>
+      <c r="H36" s="230"/>
+    </row>
+    <row r="37" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A37" s="141" t="s">
+        <v>150</v>
+      </c>
+      <c r="B37" s="141"/>
+      <c r="C37" s="141"/>
+      <c r="D37" s="141"/>
+      <c r="E37" s="141"/>
+      <c r="F37" s="141"/>
+      <c r="G37" s="141"/>
+      <c r="H37" s="74">
+        <v>2056747.63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="232" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" s="141"/>
+      <c r="C38" s="141"/>
+      <c r="D38" s="141"/>
+      <c r="E38" s="141"/>
+      <c r="F38" s="141"/>
+      <c r="G38" s="141"/>
+      <c r="H38" s="74">
+        <v>50162.18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="141" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="141"/>
+      <c r="C39" s="141"/>
+      <c r="D39" s="141"/>
+      <c r="E39" s="141"/>
+      <c r="F39" s="141"/>
+      <c r="G39" s="141"/>
+      <c r="H39" s="145">
+        <f>SUM(H37:H38)</f>
+        <v>2106909.81</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="219" t="s">
+        <v>138</v>
+      </c>
+      <c r="B40" s="219"/>
+      <c r="C40" s="219"/>
+      <c r="D40" s="219"/>
+      <c r="E40" s="219"/>
+      <c r="F40" s="219"/>
+      <c r="G40" s="219"/>
+      <c r="H40" s="219"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="81" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41" s="141"/>
+      <c r="C41" s="141"/>
+      <c r="D41" s="141"/>
+      <c r="E41" s="141"/>
+      <c r="F41" s="141"/>
+      <c r="G41" s="141"/>
+      <c r="H41" s="74">
+        <v>71200</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="141" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" s="141"/>
+      <c r="C42" s="141"/>
+      <c r="D42" s="141"/>
+      <c r="E42" s="141"/>
+      <c r="F42" s="141"/>
+      <c r="G42" s="141"/>
+      <c r="H42" s="74">
+        <v>20417</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="141" t="s">
+        <v>154</v>
+      </c>
+      <c r="B43" s="141"/>
+      <c r="C43" s="141"/>
+      <c r="D43" s="141"/>
+      <c r="E43" s="141"/>
+      <c r="F43" s="141"/>
+      <c r="G43" s="141"/>
+      <c r="H43" s="74">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="141" t="s">
+        <v>147</v>
+      </c>
+      <c r="B44" s="141"/>
+      <c r="C44" s="141"/>
+      <c r="D44" s="141"/>
+      <c r="E44" s="141"/>
+      <c r="F44" s="141"/>
+      <c r="G44" s="141"/>
+      <c r="H44" s="74">
+        <v>33150</v>
+      </c>
+      <c r="J44" s="6"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="141" t="s">
+        <v>75</v>
+      </c>
+      <c r="B45" s="141"/>
+      <c r="C45" s="141"/>
+      <c r="D45" s="141"/>
+      <c r="E45" s="141"/>
+      <c r="F45" s="141"/>
+      <c r="G45" s="141"/>
+      <c r="H45" s="70">
+        <f>SUM(H41:H44)</f>
+        <v>189767</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="219" t="s">
+        <v>139</v>
+      </c>
+      <c r="B46" s="219"/>
+      <c r="C46" s="219"/>
+      <c r="D46" s="219"/>
+      <c r="E46" s="219"/>
+      <c r="F46" s="219"/>
+      <c r="G46" s="219"/>
+      <c r="H46" s="219"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="141" t="s">
+        <v>71</v>
+      </c>
+      <c r="B47" s="141"/>
+      <c r="C47" s="141"/>
+      <c r="D47" s="141"/>
+      <c r="E47" s="141"/>
+      <c r="F47" s="141"/>
+      <c r="G47" s="141"/>
+      <c r="H47" s="74">
+        <v>148100</v>
+      </c>
+      <c r="J47" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="141" t="s">
+        <v>121</v>
+      </c>
+      <c r="B48" s="141"/>
+      <c r="C48" s="141"/>
+      <c r="D48" s="141"/>
+      <c r="E48" s="141"/>
+      <c r="F48" s="141"/>
+      <c r="G48" s="141"/>
+      <c r="H48" s="74">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="141"/>
+      <c r="B49" s="141"/>
+      <c r="C49" s="141"/>
+      <c r="D49" s="141"/>
+      <c r="E49" s="141"/>
+      <c r="F49" s="141"/>
+      <c r="G49" s="141"/>
+      <c r="H49" s="74"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="141" t="s">
+        <v>74</v>
+      </c>
+      <c r="B50" s="141"/>
+      <c r="C50" s="141"/>
+      <c r="D50" s="141"/>
+      <c r="E50" s="141"/>
+      <c r="F50" s="141"/>
+      <c r="G50" s="141"/>
+      <c r="H50" s="233">
+        <f>SUM(H47:H49)</f>
+        <v>178100</v>
+      </c>
+      <c r="K50" s="7"/>
+    </row>
+    <row r="51" spans="1:11" s="6" customFormat="1">
+      <c r="A51" s="220" t="s">
+        <v>140</v>
+      </c>
+      <c r="B51" s="221"/>
+      <c r="C51" s="221"/>
+      <c r="D51" s="221"/>
+      <c r="E51" s="221"/>
+      <c r="F51" s="221"/>
+      <c r="G51" s="221"/>
+      <c r="H51" s="222"/>
+    </row>
+    <row r="52" spans="1:11" s="6" customFormat="1">
+      <c r="A52" s="81" t="s">
+        <v>123</v>
+      </c>
+      <c r="B52" s="81"/>
+      <c r="C52" s="81"/>
+      <c r="D52" s="81"/>
+      <c r="E52" s="81"/>
+      <c r="F52" s="81"/>
+      <c r="G52" s="81"/>
+      <c r="H52" s="74">
+        <v>23006</v>
+      </c>
+      <c r="I52" s="60"/>
+    </row>
+    <row r="53" spans="1:11" s="6" customFormat="1">
+      <c r="A53" s="81" t="s">
+        <v>75</v>
+      </c>
+      <c r="B53" s="81"/>
+      <c r="C53" s="81"/>
+      <c r="D53" s="81"/>
+      <c r="E53" s="81"/>
+      <c r="F53" s="81"/>
+      <c r="G53" s="81"/>
+      <c r="H53" s="70">
+        <f>SUM(H52)</f>
+        <v>23006</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" s="6" customFormat="1">
+      <c r="A54" s="219" t="s">
+        <v>141</v>
+      </c>
+      <c r="B54" s="219"/>
+      <c r="C54" s="219"/>
+      <c r="D54" s="219"/>
+      <c r="E54" s="219"/>
+      <c r="F54" s="219"/>
+      <c r="G54" s="219"/>
+      <c r="H54" s="219"/>
+    </row>
+    <row r="55" spans="1:11" s="6" customFormat="1">
+      <c r="A55" s="81" t="s">
+        <v>151</v>
+      </c>
+      <c r="B55" s="81"/>
+      <c r="C55" s="81"/>
+      <c r="D55" s="81"/>
+      <c r="E55" s="81"/>
+      <c r="F55" s="81"/>
+      <c r="G55" s="81"/>
+      <c r="H55" s="74">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" s="6" customFormat="1">
+      <c r="A56" s="177"/>
+      <c r="B56" s="177"/>
+      <c r="C56" s="177"/>
+      <c r="D56" s="177"/>
+      <c r="E56" s="177"/>
+      <c r="F56" s="177"/>
+      <c r="G56" s="177"/>
+      <c r="H56" s="176"/>
+    </row>
+    <row r="57" spans="1:11" s="6" customFormat="1">
+      <c r="A57" s="177"/>
+      <c r="B57" s="177"/>
+      <c r="C57" s="177"/>
+      <c r="D57" s="177"/>
+      <c r="E57" s="177"/>
+      <c r="F57" s="177"/>
+      <c r="G57" s="177"/>
+      <c r="H57" s="176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A58" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="B58" s="81"/>
+      <c r="C58" s="81"/>
+      <c r="D58" s="81"/>
+      <c r="E58" s="81"/>
+      <c r="F58" s="81"/>
+      <c r="G58" s="81"/>
+      <c r="H58" s="70">
+        <f>SUM(H55:H57)</f>
+        <v>90000</v>
+      </c>
+      <c r="I58" s="60"/>
+    </row>
+    <row r="59" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A59" s="220"/>
+      <c r="B59" s="221"/>
+      <c r="C59" s="221"/>
+      <c r="D59" s="221"/>
+      <c r="E59" s="221"/>
+      <c r="F59" s="221"/>
+      <c r="G59" s="221"/>
+      <c r="H59" s="222"/>
+    </row>
+    <row r="60" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
+      <c r="A60" s="82"/>
+      <c r="B60" s="83"/>
+      <c r="C60" s="83"/>
+      <c r="D60" s="83"/>
+      <c r="E60" s="83"/>
+      <c r="F60" s="83"/>
+      <c r="G60" s="83"/>
+      <c r="H60" s="160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
+      <c r="A61" s="161"/>
+      <c r="B61" s="162"/>
+      <c r="C61" s="162"/>
+      <c r="D61" s="162"/>
+      <c r="E61" s="162"/>
+      <c r="F61" s="162"/>
+      <c r="G61" s="162"/>
+      <c r="H61" s="163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A62" s="164"/>
+      <c r="B62" s="165"/>
+      <c r="C62" s="165"/>
+      <c r="D62" s="165"/>
+      <c r="E62" s="165"/>
+      <c r="F62" s="165"/>
+      <c r="G62" s="165"/>
+      <c r="H62" s="160">
+        <f>H60+H61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A63" s="201" t="s">
+        <v>84</v>
+      </c>
+      <c r="B63" s="202"/>
+      <c r="C63" s="202"/>
+      <c r="D63" s="202"/>
+      <c r="E63" s="202"/>
+      <c r="F63" s="202"/>
+      <c r="G63" s="202"/>
+      <c r="H63" s="166">
+        <f>H58</f>
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A64" s="206"/>
+      <c r="B64" s="206"/>
+      <c r="C64" s="206"/>
+      <c r="D64" s="206"/>
+      <c r="E64" s="206"/>
+      <c r="F64" s="206"/>
+      <c r="G64" s="206"/>
+      <c r="H64" s="206"/>
+    </row>
+    <row r="65" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
+      <c r="A65" s="207"/>
+      <c r="B65" s="207"/>
+      <c r="C65" s="207"/>
+      <c r="D65" s="207"/>
+      <c r="E65" s="207"/>
+      <c r="F65" s="207"/>
+      <c r="G65" s="207"/>
+      <c r="H65" s="207"/>
+    </row>
+    <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A66" s="205" t="s">
+        <v>86</v>
+      </c>
+      <c r="B66" s="205"/>
+      <c r="C66" s="205"/>
+      <c r="D66" s="205"/>
+      <c r="E66" s="205"/>
+      <c r="F66" s="205"/>
+      <c r="G66" s="205"/>
+      <c r="H66" s="167"/>
+    </row>
+    <row r="67" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A67" s="190"/>
+      <c r="B67" s="191"/>
+      <c r="C67" s="191"/>
+      <c r="D67" s="191"/>
+      <c r="E67" s="191"/>
+      <c r="F67" s="191"/>
+      <c r="G67" s="192"/>
+      <c r="H67" s="74"/>
+    </row>
+    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A68" s="131" t="s">
+        <v>75</v>
+      </c>
+      <c r="B68" s="81"/>
+      <c r="C68" s="81"/>
+      <c r="D68" s="81"/>
+      <c r="E68" s="81"/>
+      <c r="F68" s="81"/>
+      <c r="G68" s="81"/>
+      <c r="H68" s="70">
+        <f>SUM(H67:H67)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A69" s="132"/>
+      <c r="B69" s="132"/>
+      <c r="C69" s="132"/>
+      <c r="D69" s="132"/>
+      <c r="E69" s="132"/>
+      <c r="F69" s="132"/>
+      <c r="G69" s="132"/>
+      <c r="H69" s="133"/>
+    </row>
+    <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A70" s="203" t="s">
+        <v>85</v>
+      </c>
+      <c r="B70" s="204"/>
+      <c r="C70" s="204"/>
+      <c r="D70" s="204"/>
+      <c r="E70" s="204"/>
+      <c r="F70" s="204"/>
+      <c r="G70" s="204"/>
+      <c r="H70" s="134">
+        <f>H68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A71" s="187" t="s">
+        <v>91</v>
+      </c>
+      <c r="B71" s="188"/>
+      <c r="C71" s="188"/>
+      <c r="D71" s="188"/>
+      <c r="E71" s="188"/>
+      <c r="F71" s="188"/>
+      <c r="G71" s="189"/>
+      <c r="H71" s="134"/>
+    </row>
+    <row r="72" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A72" s="187" t="s">
+        <v>96</v>
+      </c>
+      <c r="B72" s="188"/>
+      <c r="C72" s="188"/>
+      <c r="D72" s="188"/>
+      <c r="E72" s="188"/>
+      <c r="F72" s="188"/>
+      <c r="G72" s="189"/>
+      <c r="H72" s="134"/>
+    </row>
+    <row r="73" spans="1:11" ht="18.75">
+      <c r="A73" s="203" t="s">
+        <v>92</v>
+      </c>
+      <c r="B73" s="204"/>
+      <c r="C73" s="204"/>
+      <c r="D73" s="204"/>
+      <c r="E73" s="204"/>
+      <c r="F73" s="204"/>
+      <c r="G73" s="204"/>
+      <c r="H73" s="134">
+        <f>H30+H39+H45+H50+H53+H35+H18+H26</f>
+        <v>2852037.92</v>
+      </c>
+      <c r="J73" s="175"/>
+      <c r="K73" s="146"/>
+    </row>
+    <row r="74" spans="1:11" ht="18.75">
+      <c r="A74" s="196" t="s">
+        <v>126</v>
+      </c>
+      <c r="B74" s="197"/>
+      <c r="C74" s="197"/>
+      <c r="D74" s="197"/>
+      <c r="E74" s="197"/>
+      <c r="F74" s="197"/>
+      <c r="G74" s="198"/>
+      <c r="H74" s="135">
+        <f>H71+H73</f>
+        <v>2852037.92</v>
+      </c>
+      <c r="I74" s="130"/>
+      <c r="J74" s="208"/>
+      <c r="K74" s="208"/>
+    </row>
+    <row r="75" spans="1:11" ht="18.75">
+      <c r="A75" s="196" t="s">
+        <v>97</v>
+      </c>
+      <c r="B75" s="197"/>
+      <c r="C75" s="197"/>
+      <c r="D75" s="197"/>
+      <c r="E75" s="197"/>
+      <c r="F75" s="197"/>
+      <c r="G75" s="198"/>
+      <c r="H75" s="136">
+        <f>H72+H70</f>
+        <v>0</v>
+      </c>
+      <c r="J75" s="146"/>
+    </row>
+    <row r="76" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A76" s="199" t="s">
+        <v>87</v>
+      </c>
+      <c r="B76" s="200"/>
+      <c r="C76" s="200"/>
+      <c r="D76" s="200"/>
+      <c r="E76" s="200"/>
+      <c r="F76" s="200"/>
+      <c r="G76" s="200"/>
+      <c r="H76" s="137">
+        <f>H73+H70</f>
+        <v>2852037.92</v>
+      </c>
+      <c r="J76" s="7"/>
+    </row>
+    <row r="77" spans="1:11" ht="18.75" hidden="1">
+      <c r="A77" s="217" t="s">
+        <v>17</v>
+      </c>
+      <c r="B77" s="218"/>
+      <c r="C77" s="218"/>
+      <c r="D77" s="218"/>
+      <c r="E77" s="218"/>
+      <c r="F77" s="218"/>
+      <c r="G77" s="218"/>
+      <c r="H77" s="138">
+        <f>H62</f>
+        <v>0</v>
+      </c>
+      <c r="J77" s="7"/>
+    </row>
+    <row r="78" spans="1:11" ht="18.75" hidden="1">
+      <c r="A78" s="139"/>
+      <c r="B78" s="139"/>
+      <c r="C78" s="139"/>
+      <c r="D78" s="139"/>
+      <c r="E78" s="139"/>
+      <c r="F78" s="139"/>
+      <c r="G78" s="139"/>
+      <c r="H78" s="140"/>
+      <c r="J78" s="7"/>
+    </row>
+    <row r="79" spans="1:11" ht="18.75" hidden="1">
+      <c r="A79" s="139"/>
+      <c r="B79" s="139"/>
+      <c r="C79" s="139"/>
+      <c r="D79" s="139"/>
+      <c r="E79" s="139"/>
+      <c r="F79" s="139"/>
+      <c r="G79" s="139"/>
+      <c r="H79" s="140"/>
+      <c r="J79" s="7"/>
+    </row>
+    <row r="80" spans="1:11" ht="18.75" hidden="1">
+      <c r="A80" s="139"/>
+      <c r="B80" s="139"/>
+      <c r="C80" s="139"/>
+      <c r="D80" s="139"/>
+      <c r="E80" s="139"/>
+      <c r="F80" s="139"/>
+      <c r="G80" s="139"/>
+      <c r="H80" s="140"/>
+      <c r="J80" s="7"/>
+    </row>
+    <row r="81" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A81" s="141"/>
+      <c r="B81" s="141"/>
+      <c r="C81" s="141"/>
+      <c r="D81" s="141"/>
+      <c r="E81" s="141"/>
+      <c r="F81" s="141"/>
+      <c r="G81" s="141"/>
+      <c r="H81" s="141"/>
+    </row>
+    <row r="82" spans="1:11" ht="18.75">
+      <c r="A82" s="212" t="s">
+        <v>10</v>
+      </c>
+      <c r="B82" s="213"/>
+      <c r="C82" s="213"/>
+      <c r="D82" s="213"/>
+      <c r="E82" s="213"/>
+      <c r="F82" s="213"/>
+      <c r="G82" s="213"/>
+      <c r="H82" s="214"/>
+    </row>
+    <row r="83" spans="1:11" ht="18.75">
+      <c r="A83" s="142" t="s">
+        <v>12</v>
+      </c>
+      <c r="B83" s="143"/>
+      <c r="C83" s="143"/>
+      <c r="D83" s="143"/>
+      <c r="E83" s="143"/>
+      <c r="F83" s="143"/>
+      <c r="G83" s="143"/>
+      <c r="H83" s="144">
+        <v>4908824.1883903649</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" s="82" t="s">
+        <v>135</v>
+      </c>
+      <c r="B84" s="83"/>
+      <c r="C84" s="83"/>
+      <c r="D84" s="83"/>
+      <c r="E84" s="83"/>
+      <c r="F84" s="83"/>
+      <c r="G84" s="83"/>
+      <c r="H84" s="145">
+        <f>Planilla!G32</f>
+        <v>2242499.4201420001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" s="79" t="s">
+        <v>155</v>
+      </c>
+      <c r="B85" s="80"/>
+      <c r="C85" s="80"/>
+      <c r="D85" s="80"/>
+      <c r="E85" s="80"/>
+      <c r="F85" s="80"/>
+      <c r="G85" s="80"/>
+      <c r="H85" s="69">
+        <f>-(H76)</f>
+        <v>-2852037.92</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="79" t="s">
+        <v>88</v>
+      </c>
+      <c r="B86" s="80"/>
+      <c r="C86" s="80"/>
+      <c r="D86" s="80"/>
+      <c r="E86" s="80"/>
+      <c r="F86" s="80"/>
+      <c r="G86" s="80"/>
+      <c r="H86" s="69">
+        <f>-H63</f>
+        <v>-90000</v>
+      </c>
+      <c r="K86" s="6"/>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" s="79" t="s">
+        <v>73</v>
+      </c>
+      <c r="B87" s="80" t="s">
+        <v>118</v>
+      </c>
+      <c r="C87" s="80"/>
+      <c r="D87" s="80"/>
+      <c r="E87" s="80"/>
+      <c r="F87" s="80"/>
+      <c r="G87" s="80"/>
+      <c r="H87" s="125">
+        <v>133680</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" s="79" t="s">
+        <v>72</v>
+      </c>
+      <c r="B88" s="80"/>
+      <c r="C88" s="80"/>
+      <c r="D88" s="80"/>
+      <c r="E88" s="80"/>
+      <c r="F88" s="80"/>
+      <c r="G88" s="80"/>
+      <c r="H88" s="125">
+        <v>60257.527137499994</v>
+      </c>
+      <c r="I88" s="146"/>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B89" s="84"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="99"/>
+    </row>
+    <row r="90" spans="1:11" ht="18.75">
+      <c r="A90" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B90" s="23"/>
+      <c r="C90" s="23"/>
+      <c r="D90" s="23"/>
+      <c r="E90" s="23"/>
+      <c r="F90" s="23"/>
+      <c r="G90" s="23"/>
+      <c r="H90" s="85">
+        <f>SUM(H83:H89)</f>
+        <v>4403223.2156698657</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="15.75" thickBot="1"/>
+    <row r="92" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A92" s="209" t="s">
+        <v>101</v>
+      </c>
+      <c r="B92" s="210"/>
+      <c r="C92" s="210"/>
+      <c r="D92" s="210"/>
+      <c r="E92" s="210"/>
+      <c r="F92" s="210"/>
+      <c r="G92" s="210"/>
+      <c r="H92" s="211"/>
+    </row>
+    <row r="93" spans="1:11" ht="15.75">
+      <c r="A93" s="88" t="s">
+        <v>12</v>
+      </c>
+      <c r="B93" s="88"/>
+      <c r="C93" s="88"/>
+      <c r="D93" s="88"/>
+      <c r="E93" s="88"/>
+      <c r="F93" s="88"/>
+      <c r="G93" s="88"/>
+      <c r="H93" s="89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" s="61" t="s">
+        <v>125</v>
+      </c>
+      <c r="B94" s="92"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="61"/>
+      <c r="E94" s="61"/>
+      <c r="F94" s="61"/>
+      <c r="G94" s="61"/>
+      <c r="H94" s="129"/>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" s="61"/>
+      <c r="B95" s="98"/>
+      <c r="C95" s="61"/>
+      <c r="D95" s="61"/>
+      <c r="E95" s="61"/>
+      <c r="F95" s="61"/>
+      <c r="G95" s="61"/>
+      <c r="H95" s="21"/>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" s="61"/>
+      <c r="B96" s="61"/>
+      <c r="C96" s="61"/>
+      <c r="D96" s="61"/>
+      <c r="E96" s="61"/>
+      <c r="F96" s="61"/>
+      <c r="G96" s="61"/>
+      <c r="H96" s="21"/>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="86" t="s">
+        <v>11</v>
+      </c>
+      <c r="B97" s="86"/>
+      <c r="C97" s="86"/>
+      <c r="D97" s="86"/>
+      <c r="E97" s="86"/>
+      <c r="F97" s="86"/>
+      <c r="G97" s="86"/>
+      <c r="H97" s="87">
+        <f>SUM(H93:H96)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" hidden="1">
+      <c r="A100" s="194"/>
+      <c r="B100" s="194"/>
+      <c r="C100" s="194"/>
+      <c r="D100" s="194"/>
+      <c r="E100" s="194"/>
+      <c r="F100" s="194"/>
+      <c r="G100" s="194"/>
+      <c r="H100" s="194"/>
+    </row>
+    <row r="101" spans="1:8" hidden="1">
+      <c r="A101" s="194"/>
+      <c r="B101" s="194"/>
+      <c r="C101" s="194"/>
+      <c r="D101" s="194"/>
+      <c r="E101" s="194"/>
+      <c r="F101" s="194"/>
+      <c r="G101" s="194"/>
+      <c r="H101" s="194"/>
+    </row>
+    <row r="102" spans="1:8" hidden="1">
+      <c r="A102" s="194"/>
+      <c r="B102" s="194"/>
+      <c r="C102" s="194"/>
+      <c r="D102" s="194"/>
+      <c r="E102" s="194"/>
+      <c r="F102" s="194"/>
+      <c r="G102" s="194"/>
+      <c r="H102" s="194"/>
+    </row>
+    <row r="103" spans="1:8" hidden="1">
+      <c r="A103" s="194"/>
+      <c r="B103" s="194"/>
+      <c r="C103" s="194"/>
+      <c r="D103" s="194"/>
+      <c r="E103" s="194"/>
+      <c r="F103" s="194"/>
+      <c r="G103" s="194"/>
+      <c r="H103" s="194"/>
+    </row>
+  </sheetData>
+  <mergeCells count="29">
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="A100:H103"/>
+    <mergeCell ref="A92:H92"/>
+    <mergeCell ref="A82:H82"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A64:H65"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A12:H12"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
-    <col min="4" max="4" width="7.88671875" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="12.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="12.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="2" customWidth="1"/>
     <col min="10" max="10" width="11" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" customWidth="1"/>
-    <col min="14" max="14" width="15.109375" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2260,11 +3553,11 @@
         <f>RESUMEN!F8</f>
         <v>SEPTIEMBRE</v>
       </c>
-      <c r="G1" s="107" t="str">
+      <c r="G1" s="107"/>
+      <c r="H1" s="105" t="str">
         <f>RESUMEN!G8</f>
         <v>VTO: 15/10</v>
       </c>
-      <c r="H1" s="104"/>
       <c r="I1" s="104"/>
       <c r="J1" s="104"/>
       <c r="K1" s="104"/>
@@ -2337,11 +3630,11 @@
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1">
       <c r="A5" s="121"/>
-      <c r="B5" s="187">
+      <c r="B5" s="179">
         <f>C3</f>
         <v>3130261.15</v>
       </c>
-      <c r="C5" s="187"/>
+      <c r="C5" s="179"/>
       <c r="D5" s="21"/>
       <c r="E5" s="122">
         <v>70000</v>
@@ -2378,8 +3671,8 @@
     </row>
     <row r="7" spans="1:14" ht="18.75" customHeight="1">
       <c r="A7" s="121"/>
-      <c r="B7" s="187"/>
-      <c r="C7" s="187"/>
+      <c r="B7" s="179"/>
+      <c r="C7" s="179"/>
       <c r="D7" s="21"/>
       <c r="E7" s="21"/>
       <c r="F7" s="115"/>
@@ -2453,16 +3746,16 @@
         <v>4.0500000000000001E-2</v>
       </c>
       <c r="F9" s="99">
-        <v>304155.29902810499</v>
-      </c>
-      <c r="G9" s="176"/>
+        <v>446035.64516714489</v>
+      </c>
+      <c r="G9" s="223"/>
       <c r="H9" s="68">
         <f>IF(F9&gt;G9,F9-G9,0)</f>
-        <v>304155.29902810499</v>
+        <v>446035.64516714489</v>
       </c>
       <c r="I9" s="68">
         <f>H9*3.7%</f>
-        <v>11253.746064039886</v>
+        <v>16503.318871184361</v>
       </c>
       <c r="J9" s="68">
         <f>IF(G9&gt;F9,G9-F9,0)</f>
@@ -2482,7 +3775,7 @@
       </c>
       <c r="N9" s="172">
         <f>H9+I9-J9+K9+L9+M9</f>
-        <v>446035.64516714489</v>
+        <v>593165.56411332928</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -2500,11 +3793,11 @@
         <v>6.4799999999999996E-2</v>
       </c>
       <c r="F10" s="17">
-        <v>238904.50586400001</v>
-      </c>
-      <c r="G10" s="177">
+        <v>209002.56011999998</v>
+      </c>
+      <c r="G10" s="224">
         <f>F10</f>
-        <v>238904.50586400001</v>
+        <v>209002.56011999998</v>
       </c>
       <c r="H10" s="24">
         <f t="shared" ref="H10:H31" si="0">IF(F10&gt;G10,F10-G10,0)</f>
@@ -2552,11 +3845,10 @@
         <v>4.82E-2</v>
       </c>
       <c r="F11" s="99">
-        <v>177703.66022600001</v>
-      </c>
-      <c r="G11" s="177">
-        <f>F11</f>
-        <v>177703.66022600001</v>
+        <v>155461.78082999997</v>
+      </c>
+      <c r="G11" s="224">
+        <v>155500</v>
       </c>
       <c r="H11" s="68">
         <f t="shared" si="0"/>
@@ -2568,7 +3860,7 @@
       </c>
       <c r="J11" s="68">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>38.21917000002577</v>
       </c>
       <c r="K11" s="68">
         <f t="shared" si="2"/>
@@ -2584,7 +3876,7 @@
       </c>
       <c r="N11" s="172">
         <f>H11+I11-J11+K11+L11+M11+E7</f>
-        <v>155461.78082999997</v>
+        <v>155423.56165999995</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1">
@@ -2604,16 +3896,16 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F12" s="151">
-        <v>2095168.6043515448</v>
-      </c>
-      <c r="G12" s="178"/>
+        <v>2345245.9687375519</v>
+      </c>
+      <c r="G12" s="225"/>
       <c r="H12" s="152">
         <f t="shared" si="0"/>
-        <v>2095168.6043515448</v>
+        <v>2345245.9687375519</v>
       </c>
       <c r="I12" s="152">
         <f t="shared" si="6"/>
-        <v>77521.23836100717</v>
+        <v>86774.10084328943</v>
       </c>
       <c r="J12" s="152">
         <f t="shared" si="1"/>
@@ -2633,7 +3925,7 @@
       </c>
       <c r="N12" s="153">
         <f t="shared" si="5"/>
-        <v>2345245.9687375519</v>
+        <v>2604576.1956058415</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1">
@@ -2651,11 +3943,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F13" s="17">
-        <v>141941.720305</v>
-      </c>
-      <c r="G13" s="177">
+        <v>124175.90377499998</v>
+      </c>
+      <c r="G13" s="224">
         <f>F13</f>
-        <v>141941.720305</v>
+        <v>124175.90377499998</v>
       </c>
       <c r="H13" s="24">
         <f t="shared" si="0"/>
@@ -2703,11 +3995,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F14" s="17">
-        <v>132356.04568700001</v>
-      </c>
-      <c r="G14" s="177">
+        <v>115789.99858500001</v>
+      </c>
+      <c r="G14" s="224">
         <f>F14</f>
-        <v>132356.04568700001</v>
+        <v>115789.99858500001</v>
       </c>
       <c r="H14" s="24">
         <f t="shared" si="0"/>
@@ -2755,19 +4047,16 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F15" s="17">
-        <v>152633.43430199998</v>
-      </c>
-      <c r="G15" s="177">
-        <f>F15</f>
-        <v>152633.43430199998</v>
-      </c>
+        <v>133529.41340999998</v>
+      </c>
+      <c r="G15" s="224"/>
       <c r="H15" s="24">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>133529.41340999998</v>
       </c>
       <c r="I15" s="24">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4940.5882961699999</v>
       </c>
       <c r="J15" s="24">
         <f t="shared" si="1"/>
@@ -2787,7 +4076,7 @@
       </c>
       <c r="N15" s="25">
         <f t="shared" si="5"/>
-        <v>133529.41340999998</v>
+        <v>271999.41511616996</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -2807,11 +4096,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F16" s="17">
-        <v>197243.68925499998</v>
-      </c>
-      <c r="G16" s="177">
+        <v>172556.12602500001</v>
+      </c>
+      <c r="G16" s="224">
         <f>F16</f>
-        <v>197243.68925499998</v>
+        <v>172556.12602500001</v>
       </c>
       <c r="H16" s="24">
         <f t="shared" si="0"/>
@@ -2859,11 +4148,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F17" s="17">
-        <v>141941.720305</v>
-      </c>
-      <c r="G17" s="177">
+        <v>124175.90377499998</v>
+      </c>
+      <c r="G17" s="224">
         <f>F17</f>
-        <v>141941.720305</v>
+        <v>124175.90377499998</v>
       </c>
       <c r="H17" s="24">
         <f t="shared" si="0"/>
@@ -2909,18 +4198,16 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F18" s="151">
-        <v>608812.26739283314</v>
-      </c>
-      <c r="G18" s="178">
-        <v>350000</v>
-      </c>
+        <v>384178.31987136794</v>
+      </c>
+      <c r="G18" s="225"/>
       <c r="H18" s="152">
         <f>IF(F18&gt;G18,F18-G18,0)</f>
-        <v>258812.26739283314</v>
+        <v>384178.31987136794</v>
       </c>
       <c r="I18" s="152">
         <f t="shared" si="6"/>
-        <v>9576.0538935348268</v>
+        <v>14214.597835240616</v>
       </c>
       <c r="J18" s="152">
         <f t="shared" si="1"/>
@@ -2940,7 +4227,7 @@
       </c>
       <c r="N18" s="153">
         <f t="shared" si="5"/>
-        <v>384178.31987136794</v>
+        <v>514182.91629160853</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1">
@@ -2960,16 +4247,16 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F19" s="151">
-        <v>1369010.4944640244</v>
-      </c>
-      <c r="G19" s="178"/>
+        <v>1553193.2961691935</v>
+      </c>
+      <c r="G19" s="225"/>
       <c r="H19" s="152">
         <f t="shared" si="0"/>
-        <v>1369010.4944640244</v>
+        <v>1553193.2961691935</v>
       </c>
       <c r="I19" s="152">
         <f t="shared" si="6"/>
-        <v>50653.388295168908</v>
+        <v>57468.151958260169</v>
       </c>
       <c r="J19" s="152">
         <f t="shared" si="1"/>
@@ -2989,7 +4276,7 @@
       </c>
       <c r="N19" s="153">
         <f t="shared" si="5"/>
-        <v>1553193.2961691935</v>
+        <v>1744190.8615374537</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1">
@@ -3009,11 +4296,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F20" s="17">
-        <v>197243.68925499998</v>
-      </c>
-      <c r="G20" s="177">
+        <v>172556.12602500001</v>
+      </c>
+      <c r="G20" s="224">
         <f>F20</f>
-        <v>197243.68925499998</v>
+        <v>172556.12602500001</v>
       </c>
       <c r="H20" s="24">
         <f t="shared" si="0"/>
@@ -3061,18 +4348,16 @@
         <v>3.85E-2</v>
       </c>
       <c r="F21" s="151">
-        <v>812881.33862039249</v>
-      </c>
-      <c r="G21" s="179">
-        <v>145583.44</v>
-      </c>
+        <v>816163.82464434695</v>
+      </c>
+      <c r="G21" s="226"/>
       <c r="H21" s="152">
         <f t="shared" si="0"/>
-        <v>667297.89862039243</v>
+        <v>816163.82464434695</v>
       </c>
       <c r="I21" s="152">
         <f t="shared" si="6"/>
-        <v>24690.022248954523</v>
+        <v>30198.061511840842</v>
       </c>
       <c r="J21" s="152">
         <f t="shared" si="1"/>
@@ -3092,7 +4377,7 @@
       </c>
       <c r="N21" s="153">
         <f t="shared" si="5"/>
-        <v>816163.82464434695</v>
+        <v>970537.78993118776</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="15" customHeight="1">
@@ -3112,11 +4397,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F22" s="17">
-        <v>132356.04568700001</v>
-      </c>
-      <c r="G22" s="177">
+        <v>115789.99858500001</v>
+      </c>
+      <c r="G22" s="224">
         <f>F22</f>
-        <v>132356.04568700001</v>
+        <v>115789.99858500001</v>
       </c>
       <c r="H22" s="24">
         <f t="shared" si="0"/>
@@ -3164,11 +4449,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F23" s="17">
-        <v>152633.43430199998</v>
-      </c>
-      <c r="G23" s="177">
+        <v>133529.41340999998</v>
+      </c>
+      <c r="G23" s="224">
         <f>F23</f>
-        <v>152633.43430199998</v>
+        <v>133529.41340999998</v>
       </c>
       <c r="H23" s="24">
         <f t="shared" si="0"/>
@@ -3214,11 +4499,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F24" s="17">
-        <v>197243.68925499998</v>
-      </c>
-      <c r="G24" s="177">
+        <v>172556.12602500001</v>
+      </c>
+      <c r="G24" s="224">
         <f>F24</f>
-        <v>197243.68925499998</v>
+        <v>172556.12602500001</v>
       </c>
       <c r="H24" s="24">
         <f t="shared" si="0"/>
@@ -3266,11 +4551,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F25" s="17">
-        <v>141941.720305</v>
-      </c>
-      <c r="G25" s="177">
+        <v>124175.90377499998</v>
+      </c>
+      <c r="G25" s="224">
         <f>F25</f>
-        <v>141941.720305</v>
+        <v>124175.90377499998</v>
       </c>
       <c r="H25" s="24">
         <f t="shared" si="0"/>
@@ -3316,10 +4601,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F26" s="17">
-        <v>132356.04568700001</v>
-      </c>
-      <c r="G26" s="177">
-        <v>132500</v>
+        <v>115646.04427200001</v>
+      </c>
+      <c r="G26" s="224">
+        <f>F26</f>
+        <v>115646.04427200001</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="0"/>
@@ -3331,7 +4617,7 @@
       </c>
       <c r="J26" s="24">
         <f t="shared" si="1"/>
-        <v>143.95431299999473</v>
+        <v>0</v>
       </c>
       <c r="K26" s="24">
         <f t="shared" si="2"/>
@@ -3347,7 +4633,7 @@
       </c>
       <c r="N26" s="25">
         <f t="shared" si="5"/>
-        <v>115646.04427200001</v>
+        <v>115789.99858500001</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="15" customHeight="1">
@@ -3367,18 +4653,18 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F27" s="151">
-        <v>2528364.1350821592</v>
-      </c>
-      <c r="G27" s="178">
-        <v>152700</v>
+        <v>2597093.1214901991</v>
+      </c>
+      <c r="G27" s="225">
+        <v>133550</v>
       </c>
       <c r="H27" s="174">
         <f t="shared" si="0"/>
-        <v>2375664.1350821592</v>
+        <v>2463543.1214901991</v>
       </c>
       <c r="I27" s="152">
         <f t="shared" si="6"/>
-        <v>87899.572998039905</v>
+        <v>91151.095495137386</v>
       </c>
       <c r="J27" s="152">
         <f t="shared" si="1"/>
@@ -3398,7 +4684,7 @@
       </c>
       <c r="N27" s="153">
         <f t="shared" si="5"/>
-        <v>2597093.1214901991</v>
+        <v>2688223.6303953365</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="17.25" customHeight="1">
@@ -3416,16 +4702,16 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F28" s="17">
-        <v>409299.4052533551</v>
-      </c>
-      <c r="G28" s="177"/>
+        <v>591912.45477272919</v>
+      </c>
+      <c r="G28" s="224"/>
       <c r="H28" s="68">
         <f t="shared" si="0"/>
-        <v>409299.4052533551</v>
+        <v>591912.45477272919</v>
       </c>
       <c r="I28" s="24">
         <f t="shared" si="6"/>
-        <v>15144.07799437414</v>
+        <v>21900.760826590984</v>
       </c>
       <c r="J28" s="24">
         <f t="shared" si="1"/>
@@ -3442,8 +4728,9 @@
       </c>
       <c r="N28" s="25">
         <f t="shared" si="5"/>
-        <v>591912.45477272919</v>
-      </c>
+        <v>781282.18712432007</v>
+      </c>
+      <c r="O28" s="7"/>
     </row>
     <row r="29" spans="1:15" ht="15" customHeight="1">
       <c r="A29" s="51">
@@ -3460,11 +4747,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F29" s="17">
-        <v>141941.720305</v>
-      </c>
-      <c r="G29" s="177">
+        <v>124175.90377499998</v>
+      </c>
+      <c r="G29" s="224">
         <f>F29</f>
-        <v>141941.720305</v>
+        <v>124175.90377499998</v>
       </c>
       <c r="H29" s="24">
         <f t="shared" si="0"/>
@@ -3513,11 +4800,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F30" s="17">
-        <v>132356.04568700001</v>
-      </c>
-      <c r="G30" s="177">
+        <v>115789.99858500001</v>
+      </c>
+      <c r="G30" s="224">
         <f>F30</f>
-        <v>132356.04568700001</v>
+        <v>115789.99858500001</v>
       </c>
       <c r="H30" s="24">
         <f t="shared" si="0"/>
@@ -3563,11 +4850,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F31" s="17">
-        <v>152633.43430199998</v>
-      </c>
-      <c r="G31" s="177">
+        <v>133529.41340999998</v>
+      </c>
+      <c r="G31" s="224">
         <f>F31</f>
-        <v>152633.43430199998</v>
+        <v>133529.41340999998</v>
       </c>
       <c r="H31" s="24">
         <f t="shared" si="0"/>
@@ -3598,7 +4885,7 @@
         <v>133529.41340999998</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="15.6">
+    <row r="32" spans="1:15" ht="15.75">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
@@ -3612,23 +4899,23 @@
       </c>
       <c r="F32" s="100">
         <f>SUM(F9:F31)</f>
-        <v>10691122.144921415</v>
+        <v>10976263.245234534</v>
       </c>
       <c r="G32" s="100">
         <f>SUM(G9:G31)</f>
-        <v>3211857.995042</v>
+        <v>2242499.4201420001</v>
       </c>
       <c r="H32" s="126">
         <f>SUM(H9:H31)</f>
-        <v>7479408.1041924143</v>
+        <v>8733802.0442625321</v>
       </c>
       <c r="I32" s="54">
         <f>SUM(I9:I31)</f>
-        <v>276738.09985511936</v>
+        <v>323150.67563771381</v>
       </c>
       <c r="J32" s="100">
         <f t="shared" ref="J32" si="7">SUM(J9:J31)</f>
-        <v>143.95431299999473</v>
+        <v>38.21917000002577</v>
       </c>
       <c r="K32" s="91">
         <f>SUM(K9:K31)</f>
@@ -3644,117 +4931,117 @@
       </c>
       <c r="N32" s="54">
         <f>SUM(N9:N31)</f>
-        <v>10976263.245234534</v>
+        <v>12277175.496230245</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="14.25" customHeight="1"/>
     <row r="34" spans="1:14" hidden="1">
-      <c r="B34" s="186"/>
-      <c r="C34" s="186"/>
-      <c r="D34" s="186"/>
-      <c r="E34" s="186"/>
-      <c r="F34" s="186"/>
-      <c r="G34" s="186"/>
-      <c r="H34" s="186"/>
-      <c r="I34" s="186"/>
-      <c r="J34" s="186"/>
-      <c r="K34" s="186"/>
-      <c r="L34" s="186"/>
-      <c r="M34" s="186"/>
-      <c r="N34" s="186"/>
+      <c r="B34" s="178"/>
+      <c r="C34" s="178"/>
+      <c r="D34" s="178"/>
+      <c r="E34" s="178"/>
+      <c r="F34" s="178"/>
+      <c r="G34" s="178"/>
+      <c r="H34" s="178"/>
+      <c r="I34" s="178"/>
+      <c r="J34" s="178"/>
+      <c r="K34" s="178"/>
+      <c r="L34" s="178"/>
+      <c r="M34" s="178"/>
+      <c r="N34" s="178"/>
     </row>
     <row r="35" spans="1:14" hidden="1">
-      <c r="B35" s="186"/>
-      <c r="C35" s="186"/>
-      <c r="D35" s="186"/>
-      <c r="E35" s="186"/>
-      <c r="F35" s="186"/>
-      <c r="G35" s="186"/>
-      <c r="H35" s="186"/>
-      <c r="I35" s="186"/>
-      <c r="J35" s="186"/>
-      <c r="K35" s="186"/>
-      <c r="L35" s="186"/>
-      <c r="M35" s="186"/>
-      <c r="N35" s="186"/>
+      <c r="B35" s="178"/>
+      <c r="C35" s="178"/>
+      <c r="D35" s="178"/>
+      <c r="E35" s="178"/>
+      <c r="F35" s="178"/>
+      <c r="G35" s="178"/>
+      <c r="H35" s="178"/>
+      <c r="I35" s="178"/>
+      <c r="J35" s="178"/>
+      <c r="K35" s="178"/>
+      <c r="L35" s="178"/>
+      <c r="M35" s="178"/>
+      <c r="N35" s="178"/>
     </row>
     <row r="36" spans="1:14" hidden="1">
-      <c r="B36" s="186"/>
-      <c r="C36" s="186"/>
-      <c r="D36" s="186"/>
-      <c r="E36" s="186"/>
-      <c r="F36" s="186"/>
-      <c r="G36" s="186"/>
-      <c r="H36" s="186"/>
-      <c r="I36" s="186"/>
-      <c r="J36" s="186"/>
-      <c r="K36" s="186"/>
-      <c r="L36" s="186"/>
-      <c r="M36" s="186"/>
-      <c r="N36" s="186"/>
+      <c r="B36" s="178"/>
+      <c r="C36" s="178"/>
+      <c r="D36" s="178"/>
+      <c r="E36" s="178"/>
+      <c r="F36" s="178"/>
+      <c r="G36" s="178"/>
+      <c r="H36" s="178"/>
+      <c r="I36" s="178"/>
+      <c r="J36" s="178"/>
+      <c r="K36" s="178"/>
+      <c r="L36" s="178"/>
+      <c r="M36" s="178"/>
+      <c r="N36" s="178"/>
     </row>
     <row r="37" spans="1:14" hidden="1">
-      <c r="B37" s="186"/>
-      <c r="C37" s="186"/>
-      <c r="D37" s="186"/>
-      <c r="E37" s="186"/>
-      <c r="F37" s="186"/>
-      <c r="G37" s="186"/>
-      <c r="H37" s="186"/>
-      <c r="I37" s="186"/>
-      <c r="J37" s="186"/>
-      <c r="K37" s="186"/>
-      <c r="L37" s="186"/>
-      <c r="M37" s="186"/>
-      <c r="N37" s="186"/>
+      <c r="B37" s="178"/>
+      <c r="C37" s="178"/>
+      <c r="D37" s="178"/>
+      <c r="E37" s="178"/>
+      <c r="F37" s="178"/>
+      <c r="G37" s="178"/>
+      <c r="H37" s="178"/>
+      <c r="I37" s="178"/>
+      <c r="J37" s="178"/>
+      <c r="K37" s="178"/>
+      <c r="L37" s="178"/>
+      <c r="M37" s="178"/>
+      <c r="N37" s="178"/>
     </row>
     <row r="38" spans="1:14" hidden="1">
-      <c r="A38" s="188"/>
-      <c r="B38" s="188"/>
-      <c r="C38" s="188"/>
-      <c r="D38" s="188"/>
-      <c r="E38" s="188"/>
-      <c r="F38" s="188"/>
-      <c r="G38" s="188"/>
-      <c r="H38" s="188"/>
-      <c r="I38" s="188"/>
-      <c r="J38" s="188"/>
-      <c r="K38" s="188"/>
-      <c r="L38" s="188"/>
-      <c r="M38" s="188"/>
-      <c r="N38" s="188"/>
+      <c r="A38" s="180"/>
+      <c r="B38" s="180"/>
+      <c r="C38" s="180"/>
+      <c r="D38" s="180"/>
+      <c r="E38" s="180"/>
+      <c r="F38" s="180"/>
+      <c r="G38" s="180"/>
+      <c r="H38" s="180"/>
+      <c r="I38" s="180"/>
+      <c r="J38" s="180"/>
+      <c r="K38" s="180"/>
+      <c r="L38" s="180"/>
+      <c r="M38" s="180"/>
+      <c r="N38" s="180"/>
     </row>
     <row r="39" spans="1:14" hidden="1">
-      <c r="A39" s="188"/>
-      <c r="B39" s="188"/>
-      <c r="C39" s="188"/>
-      <c r="D39" s="188"/>
-      <c r="E39" s="188"/>
-      <c r="F39" s="188"/>
-      <c r="G39" s="188"/>
-      <c r="H39" s="188"/>
-      <c r="I39" s="188"/>
-      <c r="J39" s="188"/>
-      <c r="K39" s="188"/>
-      <c r="L39" s="188"/>
-      <c r="M39" s="188"/>
-      <c r="N39" s="188"/>
+      <c r="A39" s="180"/>
+      <c r="B39" s="180"/>
+      <c r="C39" s="180"/>
+      <c r="D39" s="180"/>
+      <c r="E39" s="180"/>
+      <c r="F39" s="180"/>
+      <c r="G39" s="180"/>
+      <c r="H39" s="180"/>
+      <c r="I39" s="180"/>
+      <c r="J39" s="180"/>
+      <c r="K39" s="180"/>
+      <c r="L39" s="180"/>
+      <c r="M39" s="180"/>
+      <c r="N39" s="180"/>
     </row>
     <row r="40" spans="1:14" hidden="1">
-      <c r="A40" s="188"/>
-      <c r="B40" s="188"/>
-      <c r="C40" s="188"/>
-      <c r="D40" s="188"/>
-      <c r="E40" s="188"/>
-      <c r="F40" s="188"/>
-      <c r="G40" s="188"/>
-      <c r="H40" s="188"/>
-      <c r="I40" s="188"/>
-      <c r="J40" s="188"/>
-      <c r="K40" s="188"/>
-      <c r="L40" s="188"/>
-      <c r="M40" s="188"/>
-      <c r="N40" s="188"/>
+      <c r="A40" s="180"/>
+      <c r="B40" s="180"/>
+      <c r="C40" s="180"/>
+      <c r="D40" s="180"/>
+      <c r="E40" s="180"/>
+      <c r="F40" s="180"/>
+      <c r="G40" s="180"/>
+      <c r="H40" s="180"/>
+      <c r="I40" s="180"/>
+      <c r="J40" s="180"/>
+      <c r="K40" s="180"/>
+      <c r="L40" s="180"/>
+      <c r="M40" s="180"/>
+      <c r="N40" s="180"/>
     </row>
     <row r="41" spans="1:14">
       <c r="N41" s="7"/>
@@ -3772,28 +5059,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.109375" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="189" t="s">
+      <c r="A1" s="181" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="190"/>
-      <c r="C1" s="190"/>
-      <c r="D1" s="190"/>
-      <c r="E1" s="190"/>
-      <c r="F1" s="190"/>
-      <c r="G1" s="191"/>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="182"/>
+      <c r="F1" s="182"/>
+      <c r="G1" s="183"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="30"/>
@@ -3829,13 +5116,13 @@
       <c r="C6" s="16"/>
       <c r="G6" s="31"/>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1">
       <c r="A7" s="62"/>
       <c r="B7" s="32"/>
       <c r="C7" s="16"/>
       <c r="G7" s="31"/>
     </row>
-    <row r="8" spans="1:7" ht="29.4" thickBot="1">
+    <row r="8" spans="1:7" ht="30.75" thickBot="1">
       <c r="A8" s="26" t="s">
         <v>0</v>
       </c>
@@ -4196,7 +5483,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.6">
+    <row r="24" spans="1:7" ht="15.75">
       <c r="A24" s="51">
         <v>16</v>
       </c>
@@ -4218,7 +5505,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.6">
+    <row r="25" spans="1:7" ht="15.75">
       <c r="A25" s="51">
         <v>17</v>
       </c>
@@ -4240,7 +5527,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.6">
+    <row r="26" spans="1:7" ht="15.75">
       <c r="A26" s="51">
         <v>18</v>
       </c>
@@ -4262,7 +5549,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.6">
+    <row r="27" spans="1:7" ht="15.75">
       <c r="A27" s="51">
         <v>19</v>
       </c>
@@ -4288,7 +5575,7 @@
         <v>17603.28</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.6">
+    <row r="28" spans="1:7" ht="15.75">
       <c r="A28" s="51">
         <v>20</v>
       </c>
@@ -4310,7 +5597,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.6">
+    <row r="29" spans="1:7" ht="15.75">
       <c r="A29" s="51">
         <v>21</v>
       </c>
@@ -4332,7 +5619,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.6">
+    <row r="30" spans="1:7" ht="15.75">
       <c r="A30" s="51">
         <v>22</v>
       </c>
@@ -4354,7 +5641,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.6">
+    <row r="31" spans="1:7" ht="15.75">
       <c r="A31" s="51">
         <v>23</v>
       </c>
@@ -4376,7 +5663,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.6">
+    <row r="32" spans="1:7" ht="15.75">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
@@ -4412,1352 +5699,4 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K105"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="8"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="9"/>
-    </row>
-    <row r="2" spans="1:9" ht="48" customHeight="1">
-      <c r="A2" s="10"/>
-      <c r="D2" s="228"/>
-      <c r="E2" s="229"/>
-      <c r="F2" s="229"/>
-      <c r="G2" s="229"/>
-      <c r="H2" s="230"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="10"/>
-      <c r="D3" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="200">
-        <v>1153202676</v>
-      </c>
-      <c r="F3" s="200"/>
-      <c r="G3" s="200"/>
-      <c r="H3" s="201"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="10"/>
-      <c r="D4" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="55" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="11"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="10"/>
-      <c r="D5" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="56">
-        <v>30707328890</v>
-      </c>
-      <c r="H5" s="11"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="10"/>
-      <c r="D6" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" t="s">
-        <v>119</v>
-      </c>
-      <c r="H6" s="11"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="10"/>
-      <c r="H7" s="11"/>
-    </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" ht="18">
-      <c r="A8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="90" t="s">
-        <v>155</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="H8" s="20"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="8"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="9"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="11"/>
-    </row>
-    <row r="11" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A11" s="15"/>
-      <c r="E11" s="14"/>
-      <c r="H11" s="11"/>
-    </row>
-    <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="236"/>
-      <c r="B12" s="193"/>
-      <c r="C12" s="193"/>
-      <c r="D12" s="193"/>
-      <c r="E12" s="193"/>
-      <c r="F12" s="193"/>
-      <c r="G12" s="193"/>
-      <c r="H12" s="237"/>
-    </row>
-    <row r="13" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A13" s="12"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.6">
-      <c r="A14" s="206" t="s">
-        <v>128</v>
-      </c>
-      <c r="B14" s="206"/>
-      <c r="C14" s="206"/>
-      <c r="D14" s="206"/>
-      <c r="E14" s="206"/>
-      <c r="F14" s="206"/>
-      <c r="G14" s="206"/>
-      <c r="H14" s="206"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="180" t="s">
-        <v>149</v>
-      </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="129">
-        <v>311513.3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="180" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="129">
-        <v>-49063.65</v>
-      </c>
-      <c r="I16" s="7"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="180" t="s">
-        <v>122</v>
-      </c>
-      <c r="B17" s="61"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="61"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="129">
-        <v>0.35</v>
-      </c>
-      <c r="I17" s="7"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="180" t="s">
-        <v>75</v>
-      </c>
-      <c r="B18" s="61"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="129">
-        <f>SUM(H15:H17)</f>
-        <v>262449.99999999994</v>
-      </c>
-      <c r="I18" s="7"/>
-    </row>
-    <row r="19" spans="1:9" ht="0.75" customHeight="1">
-      <c r="A19" s="232" t="s">
-        <v>132</v>
-      </c>
-      <c r="B19" s="232"/>
-      <c r="C19" s="232"/>
-      <c r="D19" s="232"/>
-      <c r="E19" s="232"/>
-      <c r="F19" s="232"/>
-      <c r="G19" s="232"/>
-      <c r="H19" s="232"/>
-    </row>
-    <row r="20" spans="1:9" hidden="1">
-      <c r="A20" s="180" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="61"/>
-      <c r="C20" s="61"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="129"/>
-    </row>
-    <row r="21" spans="1:9" hidden="1">
-      <c r="A21" s="180"/>
-      <c r="B21" s="61"/>
-      <c r="C21" s="61"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="61"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" hidden="1">
-      <c r="A22" s="180"/>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" hidden="1">
-      <c r="A23" s="180"/>
-      <c r="B23" s="61"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="61"/>
-      <c r="F23" s="61"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" hidden="1">
-      <c r="A24" s="180" t="s">
-        <v>133</v>
-      </c>
-      <c r="B24" s="61"/>
-      <c r="C24" s="61"/>
-      <c r="D24" s="61"/>
-      <c r="E24" s="61"/>
-      <c r="F24" s="61"/>
-      <c r="G24" s="61"/>
-      <c r="H24" s="129"/>
-    </row>
-    <row r="25" spans="1:9" hidden="1">
-      <c r="A25" s="180" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" s="61"/>
-      <c r="C25" s="61"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="61"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="129"/>
-    </row>
-    <row r="26" spans="1:9" hidden="1">
-      <c r="A26" s="180" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="61"/>
-      <c r="C26" s="61"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="61"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="181">
-        <f>SUM(H20:H25)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="231" t="s">
-        <v>136</v>
-      </c>
-      <c r="B27" s="231"/>
-      <c r="C27" s="231"/>
-      <c r="D27" s="231"/>
-      <c r="E27" s="231"/>
-      <c r="F27" s="231"/>
-      <c r="G27" s="231"/>
-      <c r="H27" s="231"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="61" t="s">
-        <v>145</v>
-      </c>
-      <c r="B28" s="61"/>
-      <c r="C28" s="61"/>
-      <c r="D28" s="61"/>
-      <c r="E28" s="61"/>
-      <c r="F28" s="61"/>
-      <c r="G28" s="61"/>
-      <c r="H28" s="129">
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="61"/>
-      <c r="B29" s="61"/>
-      <c r="C29" s="61"/>
-      <c r="D29" s="61"/>
-      <c r="E29" s="61"/>
-      <c r="F29" s="61"/>
-      <c r="G29" s="61"/>
-      <c r="H29" s="129"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="61" t="s">
-        <v>75</v>
-      </c>
-      <c r="B30" s="61"/>
-      <c r="C30" s="61"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="129">
-        <f>SUM(H28:H29)</f>
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A31" s="207" t="s">
-        <v>90</v>
-      </c>
-      <c r="B31" s="207"/>
-      <c r="C31" s="207"/>
-      <c r="D31" s="207"/>
-      <c r="E31" s="207"/>
-      <c r="F31" s="207"/>
-      <c r="G31" s="207"/>
-      <c r="H31" s="207"/>
-    </row>
-    <row r="32" spans="1:9" hidden="1">
-      <c r="A32" s="180"/>
-      <c r="B32" s="61"/>
-      <c r="C32" s="61"/>
-      <c r="D32" s="61"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="129"/>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="180" t="s">
-        <v>82</v>
-      </c>
-      <c r="B33" s="182"/>
-      <c r="C33" s="61"/>
-      <c r="D33" s="61"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="61"/>
-      <c r="G33" s="61"/>
-      <c r="H33" s="238">
-        <f>14146.69+1571.86+33034.56</f>
-        <v>48753.11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="61" t="s">
-        <v>146</v>
-      </c>
-      <c r="B34" s="61"/>
-      <c r="C34" s="61"/>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="61"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="61" t="s">
-        <v>74</v>
-      </c>
-      <c r="B35" s="61"/>
-      <c r="C35" s="61"/>
-      <c r="D35" s="61"/>
-      <c r="E35" s="61"/>
-      <c r="F35" s="61"/>
-      <c r="G35" s="61"/>
-      <c r="H35" s="129">
-        <f>SUM(H32:H34)</f>
-        <v>48753.11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="207" t="s">
-        <v>137</v>
-      </c>
-      <c r="B36" s="207"/>
-      <c r="C36" s="207"/>
-      <c r="D36" s="207"/>
-      <c r="E36" s="207"/>
-      <c r="F36" s="207"/>
-      <c r="G36" s="207"/>
-      <c r="H36" s="207"/>
-    </row>
-    <row r="37" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A37" s="61" t="s">
-        <v>150</v>
-      </c>
-      <c r="B37" s="61"/>
-      <c r="C37" s="61"/>
-      <c r="D37" s="61"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="129">
-        <v>2015397.65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="183" t="s">
-        <v>102</v>
-      </c>
-      <c r="B38" s="61"/>
-      <c r="C38" s="61"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="61"/>
-      <c r="H38" s="238">
-        <v>50162.18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="61" t="s">
-        <v>75</v>
-      </c>
-      <c r="B39" s="61"/>
-      <c r="C39" s="61"/>
-      <c r="D39" s="61"/>
-      <c r="E39" s="61"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="61"/>
-      <c r="H39" s="21">
-        <f>SUM(H37:H38)</f>
-        <v>2065559.8299999998</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="208" t="s">
-        <v>138</v>
-      </c>
-      <c r="B40" s="208"/>
-      <c r="C40" s="208"/>
-      <c r="D40" s="208"/>
-      <c r="E40" s="208"/>
-      <c r="F40" s="208"/>
-      <c r="G40" s="208"/>
-      <c r="H40" s="208"/>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="184" t="s">
-        <v>69</v>
-      </c>
-      <c r="B41" s="61"/>
-      <c r="C41" s="61"/>
-      <c r="D41" s="61"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="61"/>
-      <c r="H41" s="238">
-        <v>71200</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="61" t="s">
-        <v>70</v>
-      </c>
-      <c r="B42" s="61"/>
-      <c r="C42" s="61"/>
-      <c r="D42" s="61"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="61"/>
-      <c r="H42" s="238">
-        <v>20417</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="184" t="s">
-        <v>151</v>
-      </c>
-      <c r="B43" s="184"/>
-      <c r="C43" s="184"/>
-      <c r="D43" s="184"/>
-      <c r="E43" s="184"/>
-      <c r="F43" s="184"/>
-      <c r="G43" s="184"/>
-      <c r="H43" s="129">
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="61" t="s">
-        <v>156</v>
-      </c>
-      <c r="B44" s="61"/>
-      <c r="C44" s="61"/>
-      <c r="D44" s="61"/>
-      <c r="E44" s="61"/>
-      <c r="F44" s="61"/>
-      <c r="G44" s="61"/>
-      <c r="H44" s="238">
-        <v>65000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="61" t="s">
-        <v>147</v>
-      </c>
-      <c r="B45" s="61"/>
-      <c r="C45" s="61"/>
-      <c r="D45" s="61"/>
-      <c r="E45" s="61"/>
-      <c r="F45" s="61"/>
-      <c r="G45" s="61"/>
-      <c r="H45" s="238">
-        <v>33150</v>
-      </c>
-      <c r="J45" s="6"/>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="184" t="s">
-        <v>152</v>
-      </c>
-      <c r="B46" s="61"/>
-      <c r="C46" s="61"/>
-      <c r="D46" s="61"/>
-      <c r="E46" s="61"/>
-      <c r="F46" s="61"/>
-      <c r="G46" s="61"/>
-      <c r="H46" s="129">
-        <v>243400</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="61" t="s">
-        <v>75</v>
-      </c>
-      <c r="B47" s="61"/>
-      <c r="C47" s="61"/>
-      <c r="D47" s="61"/>
-      <c r="E47" s="61"/>
-      <c r="F47" s="61"/>
-      <c r="G47" s="61"/>
-      <c r="H47" s="181">
-        <f>SUM(H41:H46)</f>
-        <v>493167</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="208" t="s">
-        <v>139</v>
-      </c>
-      <c r="B48" s="208"/>
-      <c r="C48" s="208"/>
-      <c r="D48" s="208"/>
-      <c r="E48" s="208"/>
-      <c r="F48" s="208"/>
-      <c r="G48" s="208"/>
-      <c r="H48" s="208"/>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="A49" s="61" t="s">
-        <v>71</v>
-      </c>
-      <c r="B49" s="61"/>
-      <c r="C49" s="61"/>
-      <c r="D49" s="61"/>
-      <c r="E49" s="61"/>
-      <c r="F49" s="61"/>
-      <c r="G49" s="61"/>
-      <c r="H49" s="129">
-        <v>148100</v>
-      </c>
-      <c r="J49" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
-      <c r="A50" s="61" t="s">
-        <v>121</v>
-      </c>
-      <c r="B50" s="61"/>
-      <c r="C50" s="61"/>
-      <c r="D50" s="61"/>
-      <c r="E50" s="61"/>
-      <c r="F50" s="61"/>
-      <c r="G50" s="61"/>
-      <c r="H50" s="129">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
-      <c r="A51" s="61"/>
-      <c r="B51" s="61"/>
-      <c r="C51" s="61"/>
-      <c r="D51" s="61"/>
-      <c r="E51" s="61"/>
-      <c r="F51" s="61"/>
-      <c r="G51" s="61"/>
-      <c r="H51" s="129"/>
-    </row>
-    <row r="52" spans="1:11">
-      <c r="A52" s="61" t="s">
-        <v>74</v>
-      </c>
-      <c r="B52" s="61"/>
-      <c r="C52" s="61"/>
-      <c r="D52" s="61"/>
-      <c r="E52" s="61"/>
-      <c r="F52" s="61"/>
-      <c r="G52" s="61"/>
-      <c r="H52" s="185">
-        <f>SUM(H49:H51)</f>
-        <v>178100</v>
-      </c>
-      <c r="K52" s="7"/>
-    </row>
-    <row r="53" spans="1:11" s="6" customFormat="1">
-      <c r="A53" s="209" t="s">
-        <v>140</v>
-      </c>
-      <c r="B53" s="210"/>
-      <c r="C53" s="210"/>
-      <c r="D53" s="210"/>
-      <c r="E53" s="210"/>
-      <c r="F53" s="210"/>
-      <c r="G53" s="210"/>
-      <c r="H53" s="211"/>
-    </row>
-    <row r="54" spans="1:11" s="6" customFormat="1">
-      <c r="A54" s="184" t="s">
-        <v>123</v>
-      </c>
-      <c r="B54" s="184"/>
-      <c r="C54" s="184"/>
-      <c r="D54" s="184"/>
-      <c r="E54" s="184"/>
-      <c r="F54" s="184"/>
-      <c r="G54" s="184"/>
-      <c r="H54" s="238">
-        <v>23006</v>
-      </c>
-      <c r="I54" s="60"/>
-    </row>
-    <row r="55" spans="1:11" s="6" customFormat="1">
-      <c r="A55" s="184" t="s">
-        <v>75</v>
-      </c>
-      <c r="B55" s="184"/>
-      <c r="C55" s="184"/>
-      <c r="D55" s="184"/>
-      <c r="E55" s="184"/>
-      <c r="F55" s="184"/>
-      <c r="G55" s="184"/>
-      <c r="H55" s="181">
-        <f>SUM(H54)</f>
-        <v>23006</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" s="6" customFormat="1">
-      <c r="A56" s="208" t="s">
-        <v>141</v>
-      </c>
-      <c r="B56" s="208"/>
-      <c r="C56" s="208"/>
-      <c r="D56" s="208"/>
-      <c r="E56" s="208"/>
-      <c r="F56" s="208"/>
-      <c r="G56" s="208"/>
-      <c r="H56" s="208"/>
-    </row>
-    <row r="57" spans="1:11" s="6" customFormat="1">
-      <c r="A57" s="184" t="s">
-        <v>153</v>
-      </c>
-      <c r="B57" s="184"/>
-      <c r="C57" s="184"/>
-      <c r="D57" s="184"/>
-      <c r="E57" s="184"/>
-      <c r="F57" s="184"/>
-      <c r="G57" s="184"/>
-      <c r="H57" s="181">
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" s="6" customFormat="1">
-      <c r="A58" s="184"/>
-      <c r="B58" s="184"/>
-      <c r="C58" s="184"/>
-      <c r="D58" s="184"/>
-      <c r="E58" s="184"/>
-      <c r="F58" s="184"/>
-      <c r="G58" s="184"/>
-      <c r="H58" s="181"/>
-    </row>
-    <row r="59" spans="1:11" s="6" customFormat="1">
-      <c r="A59" s="184"/>
-      <c r="B59" s="184"/>
-      <c r="C59" s="184"/>
-      <c r="D59" s="184"/>
-      <c r="E59" s="184"/>
-      <c r="F59" s="184"/>
-      <c r="G59" s="184"/>
-      <c r="H59" s="181">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A60" s="81" t="s">
-        <v>76</v>
-      </c>
-      <c r="B60" s="81"/>
-      <c r="C60" s="81"/>
-      <c r="D60" s="81"/>
-      <c r="E60" s="81"/>
-      <c r="F60" s="81"/>
-      <c r="G60" s="81"/>
-      <c r="H60" s="70">
-        <f>SUM(H57:H59)</f>
-        <v>90000</v>
-      </c>
-      <c r="I60" s="60"/>
-    </row>
-    <row r="61" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A61" s="212"/>
-      <c r="B61" s="213"/>
-      <c r="C61" s="213"/>
-      <c r="D61" s="213"/>
-      <c r="E61" s="213"/>
-      <c r="F61" s="213"/>
-      <c r="G61" s="213"/>
-      <c r="H61" s="214"/>
-    </row>
-    <row r="62" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
-      <c r="A62" s="82"/>
-      <c r="B62" s="83"/>
-      <c r="C62" s="83"/>
-      <c r="D62" s="83"/>
-      <c r="E62" s="83"/>
-      <c r="F62" s="83"/>
-      <c r="G62" s="83"/>
-      <c r="H62" s="160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
-      <c r="A63" s="161"/>
-      <c r="B63" s="162"/>
-      <c r="C63" s="162"/>
-      <c r="D63" s="162"/>
-      <c r="E63" s="162"/>
-      <c r="F63" s="162"/>
-      <c r="G63" s="162"/>
-      <c r="H63" s="163">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A64" s="164"/>
-      <c r="B64" s="165"/>
-      <c r="C64" s="165"/>
-      <c r="D64" s="165"/>
-      <c r="E64" s="165"/>
-      <c r="F64" s="165"/>
-      <c r="G64" s="165"/>
-      <c r="H64" s="160">
-        <f>H62+H63</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A65" s="223" t="s">
-        <v>84</v>
-      </c>
-      <c r="B65" s="224"/>
-      <c r="C65" s="224"/>
-      <c r="D65" s="224"/>
-      <c r="E65" s="224"/>
-      <c r="F65" s="224"/>
-      <c r="G65" s="224"/>
-      <c r="H65" s="166">
-        <f>H60</f>
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A66" s="226"/>
-      <c r="B66" s="226"/>
-      <c r="C66" s="226"/>
-      <c r="D66" s="226"/>
-      <c r="E66" s="226"/>
-      <c r="F66" s="226"/>
-      <c r="G66" s="226"/>
-      <c r="H66" s="226"/>
-    </row>
-    <row r="67" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A67" s="227"/>
-      <c r="B67" s="227"/>
-      <c r="C67" s="227"/>
-      <c r="D67" s="227"/>
-      <c r="E67" s="227"/>
-      <c r="F67" s="227"/>
-      <c r="G67" s="227"/>
-      <c r="H67" s="227"/>
-    </row>
-    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A68" s="225" t="s">
-        <v>86</v>
-      </c>
-      <c r="B68" s="225"/>
-      <c r="C68" s="225"/>
-      <c r="D68" s="225"/>
-      <c r="E68" s="225"/>
-      <c r="F68" s="225"/>
-      <c r="G68" s="225"/>
-      <c r="H68" s="167"/>
-    </row>
-    <row r="69" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A69" s="233"/>
-      <c r="B69" s="234"/>
-      <c r="C69" s="234"/>
-      <c r="D69" s="234"/>
-      <c r="E69" s="234"/>
-      <c r="F69" s="234"/>
-      <c r="G69" s="235"/>
-      <c r="H69" s="74"/>
-    </row>
-    <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A70" s="131" t="s">
-        <v>75</v>
-      </c>
-      <c r="B70" s="81"/>
-      <c r="C70" s="81"/>
-      <c r="D70" s="81"/>
-      <c r="E70" s="81"/>
-      <c r="F70" s="81"/>
-      <c r="G70" s="81"/>
-      <c r="H70" s="70">
-        <f>SUM(H69:H69)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A71" s="132"/>
-      <c r="B71" s="132"/>
-      <c r="C71" s="132"/>
-      <c r="D71" s="132"/>
-      <c r="E71" s="132"/>
-      <c r="F71" s="132"/>
-      <c r="G71" s="132"/>
-      <c r="H71" s="133"/>
-    </row>
-    <row r="72" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A72" s="202" t="s">
-        <v>85</v>
-      </c>
-      <c r="B72" s="203"/>
-      <c r="C72" s="203"/>
-      <c r="D72" s="203"/>
-      <c r="E72" s="203"/>
-      <c r="F72" s="203"/>
-      <c r="G72" s="203"/>
-      <c r="H72" s="134">
-        <f>H70</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A73" s="218" t="s">
-        <v>91</v>
-      </c>
-      <c r="B73" s="219"/>
-      <c r="C73" s="219"/>
-      <c r="D73" s="219"/>
-      <c r="E73" s="219"/>
-      <c r="F73" s="219"/>
-      <c r="G73" s="220"/>
-      <c r="H73" s="134"/>
-    </row>
-    <row r="74" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A74" s="218" t="s">
-        <v>96</v>
-      </c>
-      <c r="B74" s="219"/>
-      <c r="C74" s="219"/>
-      <c r="D74" s="219"/>
-      <c r="E74" s="219"/>
-      <c r="F74" s="219"/>
-      <c r="G74" s="220"/>
-      <c r="H74" s="134"/>
-    </row>
-    <row r="75" spans="1:11" ht="18">
-      <c r="A75" s="202" t="s">
-        <v>92</v>
-      </c>
-      <c r="B75" s="203"/>
-      <c r="C75" s="203"/>
-      <c r="D75" s="203"/>
-      <c r="E75" s="203"/>
-      <c r="F75" s="203"/>
-      <c r="G75" s="203"/>
-      <c r="H75" s="134">
-        <f>H30+H39+H47+H52+H55+H35+H18+H26</f>
-        <v>3103035.94</v>
-      </c>
-      <c r="J75" s="175"/>
-      <c r="K75" s="146"/>
-    </row>
-    <row r="76" spans="1:11" ht="18">
-      <c r="A76" s="215" t="s">
-        <v>126</v>
-      </c>
-      <c r="B76" s="216"/>
-      <c r="C76" s="216"/>
-      <c r="D76" s="216"/>
-      <c r="E76" s="216"/>
-      <c r="F76" s="216"/>
-      <c r="G76" s="217"/>
-      <c r="H76" s="135">
-        <f>H73+H75</f>
-        <v>3103035.94</v>
-      </c>
-      <c r="I76" s="130"/>
-      <c r="J76" s="192"/>
-      <c r="K76" s="192"/>
-    </row>
-    <row r="77" spans="1:11" ht="18">
-      <c r="A77" s="215" t="s">
-        <v>97</v>
-      </c>
-      <c r="B77" s="216"/>
-      <c r="C77" s="216"/>
-      <c r="D77" s="216"/>
-      <c r="E77" s="216"/>
-      <c r="F77" s="216"/>
-      <c r="G77" s="217"/>
-      <c r="H77" s="136">
-        <f>H74+H72</f>
-        <v>0</v>
-      </c>
-      <c r="J77" s="146"/>
-    </row>
-    <row r="78" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A78" s="221" t="s">
-        <v>87</v>
-      </c>
-      <c r="B78" s="222"/>
-      <c r="C78" s="222"/>
-      <c r="D78" s="222"/>
-      <c r="E78" s="222"/>
-      <c r="F78" s="222"/>
-      <c r="G78" s="222"/>
-      <c r="H78" s="137">
-        <f>H75+H72</f>
-        <v>3103035.94</v>
-      </c>
-      <c r="J78" s="7"/>
-    </row>
-    <row r="79" spans="1:11" ht="18" hidden="1">
-      <c r="A79" s="204" t="s">
-        <v>17</v>
-      </c>
-      <c r="B79" s="205"/>
-      <c r="C79" s="205"/>
-      <c r="D79" s="205"/>
-      <c r="E79" s="205"/>
-      <c r="F79" s="205"/>
-      <c r="G79" s="205"/>
-      <c r="H79" s="138">
-        <f>H64</f>
-        <v>0</v>
-      </c>
-      <c r="J79" s="7"/>
-    </row>
-    <row r="80" spans="1:11" ht="18" hidden="1">
-      <c r="A80" s="139"/>
-      <c r="B80" s="139"/>
-      <c r="C80" s="139"/>
-      <c r="D80" s="139"/>
-      <c r="E80" s="139"/>
-      <c r="F80" s="139"/>
-      <c r="G80" s="139"/>
-      <c r="H80" s="140"/>
-      <c r="J80" s="7"/>
-    </row>
-    <row r="81" spans="1:11" ht="18" hidden="1">
-      <c r="A81" s="139"/>
-      <c r="B81" s="139"/>
-      <c r="C81" s="139"/>
-      <c r="D81" s="139"/>
-      <c r="E81" s="139"/>
-      <c r="F81" s="139"/>
-      <c r="G81" s="139"/>
-      <c r="H81" s="140"/>
-      <c r="J81" s="7"/>
-    </row>
-    <row r="82" spans="1:11" ht="18" hidden="1">
-      <c r="A82" s="139"/>
-      <c r="B82" s="139"/>
-      <c r="C82" s="139"/>
-      <c r="D82" s="139"/>
-      <c r="E82" s="139"/>
-      <c r="F82" s="139"/>
-      <c r="G82" s="139"/>
-      <c r="H82" s="140"/>
-      <c r="J82" s="7"/>
-    </row>
-    <row r="83" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A83" s="141"/>
-      <c r="B83" s="141"/>
-      <c r="C83" s="141"/>
-      <c r="D83" s="141"/>
-      <c r="E83" s="141"/>
-      <c r="F83" s="141"/>
-      <c r="G83" s="141"/>
-      <c r="H83" s="141"/>
-    </row>
-    <row r="84" spans="1:11" ht="18">
-      <c r="A84" s="197" t="s">
-        <v>10</v>
-      </c>
-      <c r="B84" s="198"/>
-      <c r="C84" s="198"/>
-      <c r="D84" s="198"/>
-      <c r="E84" s="198"/>
-      <c r="F84" s="198"/>
-      <c r="G84" s="198"/>
-      <c r="H84" s="199"/>
-    </row>
-    <row r="85" spans="1:11" ht="18">
-      <c r="A85" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="B85" s="143"/>
-      <c r="C85" s="143"/>
-      <c r="D85" s="143"/>
-      <c r="E85" s="143"/>
-      <c r="F85" s="143"/>
-      <c r="G85" s="143"/>
-      <c r="H85" s="144">
-        <v>4747227.3433483643</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11">
-      <c r="A86" s="82" t="s">
-        <v>135</v>
-      </c>
-      <c r="B86" s="83"/>
-      <c r="C86" s="83"/>
-      <c r="D86" s="83"/>
-      <c r="E86" s="83"/>
-      <c r="F86" s="83"/>
-      <c r="G86" s="83"/>
-      <c r="H86" s="145">
-        <f>Planilla!G32</f>
-        <v>3211857.995042</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11">
-      <c r="A87" s="79" t="s">
-        <v>157</v>
-      </c>
-      <c r="B87" s="80"/>
-      <c r="C87" s="80"/>
-      <c r="D87" s="80"/>
-      <c r="E87" s="80"/>
-      <c r="F87" s="80"/>
-      <c r="G87" s="80"/>
-      <c r="H87" s="69">
-        <f>-(H78)</f>
-        <v>-3103035.94</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11">
-      <c r="A88" s="79" t="s">
-        <v>88</v>
-      </c>
-      <c r="B88" s="80"/>
-      <c r="C88" s="80"/>
-      <c r="D88" s="80"/>
-      <c r="E88" s="80"/>
-      <c r="F88" s="80"/>
-      <c r="G88" s="80"/>
-      <c r="H88" s="69">
-        <f>-H65</f>
-        <v>-90000</v>
-      </c>
-      <c r="K88" s="6"/>
-    </row>
-    <row r="89" spans="1:11">
-      <c r="A89" s="79" t="s">
-        <v>73</v>
-      </c>
-      <c r="B89" s="80" t="s">
-        <v>118</v>
-      </c>
-      <c r="C89" s="80"/>
-      <c r="D89" s="80"/>
-      <c r="E89" s="80"/>
-      <c r="F89" s="80"/>
-      <c r="G89" s="80"/>
-      <c r="H89" s="125">
-        <f>170000-H90</f>
-        <v>133680</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11">
-      <c r="A90" s="79" t="s">
-        <v>72</v>
-      </c>
-      <c r="B90" s="80"/>
-      <c r="C90" s="80"/>
-      <c r="D90" s="80"/>
-      <c r="E90" s="80"/>
-      <c r="F90" s="80"/>
-      <c r="G90" s="80"/>
-      <c r="H90" s="125">
-        <v>36320</v>
-      </c>
-      <c r="I90" s="146"/>
-    </row>
-    <row r="91" spans="1:11">
-      <c r="A91" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="B91" s="84"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="99"/>
-    </row>
-    <row r="92" spans="1:11" ht="18">
-      <c r="A92" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="B92" s="23"/>
-      <c r="C92" s="23"/>
-      <c r="D92" s="23"/>
-      <c r="E92" s="23"/>
-      <c r="F92" s="23"/>
-      <c r="G92" s="23"/>
-      <c r="H92" s="85">
-        <f>SUM(H85:H91)</f>
-        <v>4936049.3983903639</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" ht="15" thickBot="1"/>
-    <row r="94" spans="1:11" ht="16.2" thickBot="1">
-      <c r="A94" s="194" t="s">
-        <v>101</v>
-      </c>
-      <c r="B94" s="195"/>
-      <c r="C94" s="195"/>
-      <c r="D94" s="195"/>
-      <c r="E94" s="195"/>
-      <c r="F94" s="195"/>
-      <c r="G94" s="195"/>
-      <c r="H94" s="196"/>
-    </row>
-    <row r="95" spans="1:11" ht="15.6">
-      <c r="A95" s="88" t="s">
-        <v>12</v>
-      </c>
-      <c r="B95" s="88"/>
-      <c r="C95" s="88"/>
-      <c r="D95" s="88"/>
-      <c r="E95" s="88"/>
-      <c r="F95" s="88"/>
-      <c r="G95" s="88"/>
-      <c r="H95" s="89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11">
-      <c r="A96" s="61" t="s">
-        <v>125</v>
-      </c>
-      <c r="B96" s="92"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="61"/>
-      <c r="E96" s="61"/>
-      <c r="F96" s="61"/>
-      <c r="G96" s="61"/>
-      <c r="H96" s="129"/>
-    </row>
-    <row r="97" spans="1:8">
-      <c r="A97" s="61"/>
-      <c r="B97" s="98"/>
-      <c r="C97" s="61"/>
-      <c r="D97" s="61"/>
-      <c r="E97" s="61"/>
-      <c r="F97" s="61"/>
-      <c r="G97" s="61"/>
-      <c r="H97" s="21"/>
-    </row>
-    <row r="98" spans="1:8">
-      <c r="A98" s="61"/>
-      <c r="B98" s="61"/>
-      <c r="C98" s="61"/>
-      <c r="D98" s="61"/>
-      <c r="E98" s="61"/>
-      <c r="F98" s="61"/>
-      <c r="G98" s="61"/>
-      <c r="H98" s="21"/>
-    </row>
-    <row r="99" spans="1:8">
-      <c r="A99" s="86" t="s">
-        <v>11</v>
-      </c>
-      <c r="B99" s="86"/>
-      <c r="C99" s="86"/>
-      <c r="D99" s="86"/>
-      <c r="E99" s="86"/>
-      <c r="F99" s="86"/>
-      <c r="G99" s="86"/>
-      <c r="H99" s="87">
-        <f>SUM(H95:H98)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" hidden="1">
-      <c r="A102" s="193"/>
-      <c r="B102" s="193"/>
-      <c r="C102" s="193"/>
-      <c r="D102" s="193"/>
-      <c r="E102" s="193"/>
-      <c r="F102" s="193"/>
-      <c r="G102" s="193"/>
-      <c r="H102" s="193"/>
-    </row>
-    <row r="103" spans="1:8" hidden="1">
-      <c r="A103" s="193"/>
-      <c r="B103" s="193"/>
-      <c r="C103" s="193"/>
-      <c r="D103" s="193"/>
-      <c r="E103" s="193"/>
-      <c r="F103" s="193"/>
-      <c r="G103" s="193"/>
-      <c r="H103" s="193"/>
-    </row>
-    <row r="104" spans="1:8" hidden="1">
-      <c r="A104" s="193"/>
-      <c r="B104" s="193"/>
-      <c r="C104" s="193"/>
-      <c r="D104" s="193"/>
-      <c r="E104" s="193"/>
-      <c r="F104" s="193"/>
-      <c r="G104" s="193"/>
-      <c r="H104" s="193"/>
-    </row>
-    <row r="105" spans="1:8" hidden="1">
-      <c r="A105" s="193"/>
-      <c r="B105" s="193"/>
-      <c r="C105" s="193"/>
-      <c r="D105" s="193"/>
-      <c r="E105" s="193"/>
-      <c r="F105" s="193"/>
-      <c r="G105" s="193"/>
-      <c r="H105" s="193"/>
-    </row>
-  </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A69:G69"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A76:G76"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="A65:G65"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A68:G68"/>
-    <mergeCell ref="A66:H67"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="A102:H105"/>
-    <mergeCell ref="A94:H94"/>
-    <mergeCell ref="A84:H84"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="A75:G75"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A73:G73"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>